--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_18sep26_Fri.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_18sep26_Fri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1396327F-EEAF-4F1F-812C-C6E92AA942C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ED7E03-1008-47F5-9977-466809FC989C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Sheet1 (2)" sheetId="15" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sheet1 (2)'!$A$1:$P$296</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$L$8</definedName>
   </definedNames>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3455" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3460" uniqueCount="316">
   <si>
     <t>Date</t>
   </si>
@@ -1145,7 +1145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1332,31 +1332,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1661,7 +1637,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P295"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1765,7 +1740,7 @@
         <v>300.90000000000009</v>
       </c>
       <c r="N2" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B2, $C$2:$C$734, C2, $D$2:$D$734, D2, $E$2:$E$734, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N33" si="0">IF(COUNTIFS( $B$2:$B$734, B2, $C$2:$C$734, C2, $D$2:$D$734, D2, $E$2:$E$734, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -1806,7 +1781,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B3, $C$2:$C$734, C3, $D$2:$D$734, D3, $E$2:$E$734, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -1847,7 +1822,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B4, $C$2:$C$734, C4, $D$2:$D$734, D4, $E$2:$E$734, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -1888,7 +1863,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B5, $C$2:$C$734, C5, $D$2:$D$734, D5, $E$2:$E$734, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -1929,7 +1904,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B6, $C$2:$C$734, C6, $D$2:$D$734, D6, $E$2:$E$734, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1968,7 +1943,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B7, $C$2:$C$734, C7, $D$2:$D$734, D7, $E$2:$E$734, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
@@ -2007,7 +1982,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B8, $C$2:$C$734, C8, $D$2:$D$734, D8, $E$2:$E$734, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="26"/>
@@ -2055,7 +2030,7 @@
         <v>34175</v>
       </c>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B9, $C$2:$C$734, C9, $D$2:$D$734, D9, $E$2:$E$734, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
@@ -2094,7 +2069,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B10, $C$2:$C$734, C10, $D$2:$D$734, D10, $E$2:$E$734, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="19"/>
@@ -2142,7 +2117,7 @@
         <v>460</v>
       </c>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B11, $C$2:$C$734, C11, $D$2:$D$734, D11, $E$2:$E$734, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P11" s="10"/>
@@ -2180,7 +2155,7 @@
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B12, $C$2:$C$734, C12, $D$2:$D$734, D12, $E$2:$E$734, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2217,7 +2192,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B13, $C$2:$C$734, C13, $D$2:$D$734, D13, $E$2:$E$734, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="10"/>
@@ -2265,7 +2240,7 @@
         <v>300</v>
       </c>
       <c r="N14" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B14, $C$2:$C$734, C14, $D$2:$D$734, D14, $E$2:$E$734, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O14" s="31"/>
@@ -2313,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="N15" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B15, $C$2:$C$734, C15, $D$2:$D$734, D15, $E$2:$E$734, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O15" s="31"/>
@@ -2361,7 +2336,7 @@
         <v>200</v>
       </c>
       <c r="N16" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B16, $C$2:$C$734, C16, $D$2:$D$734, D16, $E$2:$E$734, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O16" s="31"/>
@@ -2409,7 +2384,7 @@
         <v>300</v>
       </c>
       <c r="N17" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B17, $C$2:$C$734, C17, $D$2:$D$734, D17, $E$2:$E$734, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O17" s="10"/>
@@ -2457,7 +2432,7 @@
         <v>300</v>
       </c>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B18, $C$2:$C$734, C18, $D$2:$D$734, D18, $E$2:$E$734, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O18" s="10"/>
@@ -2498,7 +2473,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B19, $C$2:$C$734, C19, $D$2:$D$734, D19, $E$2:$E$734, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19" s="10"/>
@@ -2537,7 +2512,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B20, $C$2:$C$734, C20, $D$2:$D$734, D20, $E$2:$E$734, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20" s="10"/>
@@ -2585,7 +2560,7 @@
         <v>300</v>
       </c>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B21, $C$2:$C$734, C21, $D$2:$D$734, D21, $E$2:$E$734, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="10"/>
@@ -2633,7 +2608,7 @@
         <v>300</v>
       </c>
       <c r="N22" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B22, $C$2:$C$734, C22, $D$2:$D$734, D22, $E$2:$E$734, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22" s="10"/>
@@ -2674,7 +2649,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B23, $C$2:$C$734, C23, $D$2:$D$734, D23, $E$2:$E$734, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23" s="30"/>
@@ -2714,7 +2689,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B24, $C$2:$C$734, C24, $D$2:$D$734, D24, $E$2:$E$734, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24" s="10"/>
@@ -2753,7 +2728,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B25, $C$2:$C$734, C25, $D$2:$D$734, D25, $E$2:$E$734, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P25" s="10"/>
@@ -2800,7 +2775,7 @@
         <v>720</v>
       </c>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B26, $C$2:$C$734, C26, $D$2:$D$734, D26, $E$2:$E$734, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2839,7 +2814,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B27, $C$2:$C$734, C27, $D$2:$D$734, D27, $E$2:$E$734, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27"/>
@@ -2880,7 +2855,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B28, $C$2:$C$734, C28, $D$2:$D$734, D28, $E$2:$E$734, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28"/>
@@ -2921,7 +2896,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B29, $C$2:$C$734, C29, $D$2:$D$734, D29, $E$2:$E$734, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29"/>
@@ -2960,7 +2935,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B30, $C$2:$C$734, C30, $D$2:$D$734, D30, $E$2:$E$734, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30"/>
@@ -3002,7 +2977,7 @@
         <v>3156</v>
       </c>
       <c r="N31" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B31, $C$2:$C$734, C31, $D$2:$D$734, D31, $E$2:$E$734, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P31" s="19"/>
@@ -3042,7 +3017,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B32, $C$2:$C$734, C32, $D$2:$D$734, D32, $E$2:$E$734, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32"/>
@@ -3083,7 +3058,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B33, $C$2:$C$734, C33, $D$2:$D$734, D33, $E$2:$E$734, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3129,7 +3104,7 @@
         <v>516</v>
       </c>
       <c r="N34" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B34, $C$2:$C$734, C34, $D$2:$D$734, D34, $E$2:$E$734, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N34:N69" si="1">IF(COUNTIFS( $B$2:$B$734, B34, $C$2:$C$734, C34, $D$2:$D$734, D34, $E$2:$E$734, E34) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -3175,7 +3150,7 @@
         <v>300</v>
       </c>
       <c r="N35" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B35, $C$2:$C$734, C35, $D$2:$D$734, D35, $E$2:$E$734, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P35" s="25"/>
@@ -3222,7 +3197,7 @@
         <v>500</v>
       </c>
       <c r="N36" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B36, $C$2:$C$734, C36, $D$2:$D$734, D36, $E$2:$E$734, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O36" s="10"/>
@@ -3270,7 +3245,7 @@
         <v>525</v>
       </c>
       <c r="N37" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B37, $C$2:$C$734, C37, $D$2:$D$734, D37, $E$2:$E$734, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3307,7 +3282,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B38, $C$2:$C$734, C38, $D$2:$D$734, D38, $E$2:$E$734, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O38"/>
@@ -3348,7 +3323,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B39, $C$2:$C$734, C39, $D$2:$D$734, D39, $E$2:$E$734, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3387,7 +3362,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B40, $C$2:$C$734, C40, $D$2:$D$734, D40, $E$2:$E$734, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O40"/>
@@ -3435,7 +3410,7 @@
         <v>300</v>
       </c>
       <c r="N41" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B41, $C$2:$C$734, C41, $D$2:$D$734, D41, $E$2:$E$734, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
@@ -3474,7 +3449,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B42, $C$2:$C$734, C42, $D$2:$D$734, D42, $E$2:$E$734, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
@@ -3514,7 +3489,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B43, $C$2:$C$734, C43, $D$2:$D$734, D43, $E$2:$E$734, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O43"/>
@@ -3555,7 +3530,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B44, $C$2:$C$734, C44, $D$2:$D$734, D44, $E$2:$E$734, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
@@ -3594,7 +3569,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B45, $C$2:$C$734, C45, $D$2:$D$734, D45, $E$2:$E$734, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -3635,7 +3610,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B46, $C$2:$C$734, C46, $D$2:$D$734, D46, $E$2:$E$734, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -3676,7 +3651,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B47, $C$2:$C$734, C47, $D$2:$D$734, D47, $E$2:$E$734, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -3717,7 +3692,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B48, $C$2:$C$734, C48, $D$2:$D$734, D48, $E$2:$E$734, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P48"/>
@@ -3755,7 +3730,7 @@
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B49, $C$2:$C$734, C49, $D$2:$D$734, D49, $E$2:$E$734, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O49"/>
@@ -3804,7 +3779,7 @@
         <v>540</v>
       </c>
       <c r="N50" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B50, $C$2:$C$734, C50, $D$2:$D$734, D50, $E$2:$E$734, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O50"/>
@@ -3852,7 +3827,7 @@
         <v>10680</v>
       </c>
       <c r="N51" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B51, $C$2:$C$734, C51, $D$2:$D$734, D51, $E$2:$E$734, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O51" s="10"/>
@@ -3893,7 +3868,7 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B52, $C$2:$C$734, C52, $D$2:$D$734, D52, $E$2:$E$734, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O52"/>
@@ -3931,7 +3906,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B53, $C$2:$C$734, C53, $D$2:$D$734, D53, $E$2:$E$734, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O53"/>
@@ -3974,7 +3949,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B54, $C$2:$C$734, C54, $D$2:$D$734, D54, $E$2:$E$734, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -4013,7 +3988,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B55, $C$2:$C$734, C55, $D$2:$D$734, D55, $E$2:$E$734, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -4054,7 +4029,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B56, $C$2:$C$734, C56, $D$2:$D$734, D56, $E$2:$E$734, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
@@ -4095,7 +4070,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B57, $C$2:$C$734, C57, $D$2:$D$734, D57, $E$2:$E$734, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -4136,7 +4111,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B58, $C$2:$C$734, C58, $D$2:$D$734, D58, $E$2:$E$734, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -4175,7 +4150,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B59, $C$2:$C$734, C59, $D$2:$D$734, D59, $E$2:$E$734, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O59"/>
@@ -4214,7 +4189,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B60, $C$2:$C$734, C60, $D$2:$D$734, D60, $E$2:$E$734, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O60"/>
@@ -4253,7 +4228,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B61, $C$2:$C$734, C61, $D$2:$D$734, D61, $E$2:$E$734, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O61"/>
@@ -4292,7 +4267,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B62, $C$2:$C$734, C62, $D$2:$D$734, D62, $E$2:$E$734, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O62"/>
@@ -4340,7 +4315,7 @@
         <v>10880</v>
       </c>
       <c r="N63" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B63, $C$2:$C$734, C63, $D$2:$D$734, D63, $E$2:$E$734, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O63" s="10"/>
@@ -4379,7 +4354,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B64, $C$2:$C$734, C64, $D$2:$D$734, D64, $E$2:$E$734, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -4418,7 +4393,7 @@
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B65, $C$2:$C$734, C65, $D$2:$D$734, D65, $E$2:$E$734, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O65"/>
@@ -4452,12 +4427,12 @@
       <c r="I66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="71"/>
+      <c r="J66" s="52"/>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B66, $C$2:$C$734, C66, $D$2:$D$734, D66, $E$2:$E$734, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4489,14 +4464,14 @@
       <c r="I67" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J67" s="71" t="s">
+      <c r="J67" s="52" t="s">
         <v>41</v>
       </c>
       <c r="K67" s="17"/>
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B67, $C$2:$C$734, C67, $D$2:$D$734, D67, $E$2:$E$734, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4528,12 +4503,12 @@
       <c r="I68" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J68" s="71"/>
+      <c r="J68" s="52"/>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B68, $C$2:$C$734, C68, $D$2:$D$734, D68, $E$2:$E$734, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4565,14 +4540,14 @@
       <c r="I69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="71" t="s">
+      <c r="J69" s="52" t="s">
         <v>41</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B69, $C$2:$C$734, C69, $D$2:$D$734, D69, $E$2:$E$734, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4604,18 +4579,18 @@
       <c r="I70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J70" s="72" t="s">
+      <c r="J70" s="64" t="s">
         <v>41</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B70, $C$2:$C$734, C70, $D$2:$D$734, D70, $E$2:$E$734, E70) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="N70" si="2">IF(COUNTIFS( $B$2:$B$734, B70, $C$2:$C$734, C70, $D$2:$D$734, D70, $E$2:$E$734, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="3">
         <v>46268.375</v>
       </c>
@@ -4657,7 +4632,7 @@
         <v>1200</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B71, $C$2:$C$734, C71, $D$2:$D$734, D71, $E$2:$E$734, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N71:N134" si="3">IF(COUNTIFS( $B$2:$B$734, B71, $C$2:$C$734, C71, $D$2:$D$734, D71, $E$2:$E$734, E71) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O71" s="10"/>
@@ -4691,16 +4666,16 @@
       <c r="I72" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J72" s="71"/>
+      <c r="J72" s="52"/>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B72, $C$2:$C$734, C72, $D$2:$D$734, D72, $E$2:$E$734, E72) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="32">
         <v>46262.375</v>
       </c>
@@ -4742,7 +4717,7 @@
         <v>175</v>
       </c>
       <c r="N73" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B73, $C$2:$C$734, C73, $D$2:$D$734, D73, $E$2:$E$734, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O73" s="41" t="s">
@@ -4750,7 +4725,7 @@
       </c>
       <c r="P73"/>
     </row>
-    <row r="74" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="32">
         <v>46265.375694444447</v>
       </c>
@@ -4792,7 +4767,7 @@
         <v>225</v>
       </c>
       <c r="N74" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B74, $C$2:$C$734, C74, $D$2:$D$734, D74, $E$2:$E$734, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O74" s="41" t="s">
@@ -4828,20 +4803,20 @@
       <c r="I75" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J75" s="71" t="s">
+      <c r="J75" s="52" t="s">
         <v>55</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
       <c r="N75" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B75, $C$2:$C$734, C75, $D$2:$D$734, D75, $E$2:$E$734, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O75"/>
       <c r="P75"/>
     </row>
-    <row r="76" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="3">
         <v>46267.461111111108</v>
       </c>
@@ -4883,7 +4858,7 @@
         <v>1000</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B76, $C$2:$C$734, C76, $D$2:$D$734, D76, $E$2:$E$734, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4915,20 +4890,20 @@
       <c r="I77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J77" s="71" t="s">
+      <c r="J77" s="52" t="s">
         <v>41</v>
       </c>
       <c r="K77" s="17"/>
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B77, $C$2:$C$734, C77, $D$2:$D$734, D77, $E$2:$E$734, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O77"/>
       <c r="P77"/>
     </row>
-    <row r="78" spans="1:16" s="26" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:16" s="26" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="3">
         <v>46281.376388888886</v>
       </c>
@@ -4970,13 +4945,13 @@
         <v>300</v>
       </c>
       <c r="N78" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B78, $C$2:$C$734, C78, $D$2:$D$734, D78, $E$2:$E$734, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O78" s="10"/>
       <c r="P78" s="10"/>
     </row>
-    <row r="79" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="3">
         <v>46275.375</v>
       </c>
@@ -5018,11 +4993,11 @@
         <v>300</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B79, $C$2:$C$734, C79, $D$2:$D$734, D79, $E$2:$E$734, E79) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="3">
         <v>46267.375</v>
       </c>
@@ -5064,14 +5039,14 @@
         <v>360</v>
       </c>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B80, $C$2:$C$734, C80, $D$2:$D$734, D80, $E$2:$E$734, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O80" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="11">
         <v>46273.375</v>
       </c>
@@ -5113,8 +5088,11 @@
         <v>200</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B81, $C$2:$C$734, C81, $D$2:$D$734, D81, $E$2:$E$734, E81) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+      <c r="O81" s="41" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -5145,20 +5123,20 @@
       <c r="I82" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J82" s="71" t="s">
+      <c r="J82" s="52" t="s">
         <v>41</v>
       </c>
       <c r="K82" s="17"/>
       <c r="L82" s="17"/>
       <c r="M82" s="17"/>
       <c r="N82" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B82, $C$2:$C$734, C82, $D$2:$D$734, D82, $E$2:$E$734, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O82"/>
       <c r="P82"/>
     </row>
-    <row r="83" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="3">
         <v>46280.435416666667</v>
       </c>
@@ -5200,11 +5178,11 @@
         <v>18850</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B83, $C$2:$C$734, C83, $D$2:$D$734, D83, $E$2:$E$734, E83) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="3">
         <v>46276.375</v>
       </c>
@@ -5246,11 +5224,11 @@
         <v>646</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B84, $C$2:$C$734, C84, $D$2:$D$734, D84, $E$2:$E$734, E84) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="3">
         <v>46267.375</v>
       </c>
@@ -5292,11 +5270,11 @@
         <v>295</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B85, $C$2:$C$734, C85, $D$2:$D$734, D85, $E$2:$E$734, E85) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" s="26" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" s="26" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="8" t="s">
         <v>62</v>
       </c>
@@ -5329,13 +5307,13 @@
       <c r="L86" s="18"/>
       <c r="M86" s="18"/>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B86, $C$2:$C$734, C86, $D$2:$D$734, D86, $E$2:$E$734, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O86" s="10"/>
       <c r="P86" s="10"/>
     </row>
-    <row r="87" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="3">
         <v>46280.375694444447</v>
       </c>
@@ -5373,18 +5351,18 @@
         <v>8320</v>
       </c>
       <c r="M87" s="18">
-        <f>ABS((D87*E87)-L87)</f>
+        <f t="shared" ref="M87:M103" si="4">ABS((D87*E87)-L87)</f>
         <v>650</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B87, $C$2:$C$734, C87, $D$2:$D$734, D87, $E$2:$E$734, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O87" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="32">
         <v>46281.443055555559</v>
       </c>
@@ -5422,11 +5400,11 @@
         <v>5585</v>
       </c>
       <c r="M88" s="29">
-        <f>ABS((D88*E88)-L88)</f>
+        <f t="shared" si="4"/>
         <v>395</v>
       </c>
       <c r="N88" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B88, $C$2:$C$734, C88, $D$2:$D$734, D88, $E$2:$E$734, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O88" s="41" t="s">
@@ -5434,7 +5412,7 @@
       </c>
       <c r="P88" s="31"/>
     </row>
-    <row r="89" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="32">
         <v>46281.388888888891</v>
       </c>
@@ -5472,18 +5450,18 @@
         <v>5730</v>
       </c>
       <c r="M89" s="29">
-        <f>ABS((D89*E89)-L89)</f>
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="N89" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B89, $C$2:$C$734, C89, $D$2:$D$734, D89, $E$2:$E$734, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O89" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="90" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="11">
         <v>46273.375</v>
       </c>
@@ -5521,17 +5499,17 @@
         <v>9170</v>
       </c>
       <c r="M90" s="29">
-        <f>ABS((D90*E90)-L90)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B90, $C$2:$C$734, C90, $D$2:$D$734, D90, $E$2:$E$734, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="10"/>
       <c r="P90" s="10"/>
     </row>
-    <row r="91" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="3">
         <v>46276.375</v>
       </c>
@@ -5569,15 +5547,15 @@
         <v>11320</v>
       </c>
       <c r="M91" s="18">
-        <f>ABS((D91*E91)-L91)</f>
+        <f t="shared" si="4"/>
         <v>400</v>
       </c>
       <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B91, $C$2:$C$734, C91, $D$2:$D$734, D91, $E$2:$E$734, E91) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="43">
         <v>46273.375</v>
       </c>
@@ -5615,11 +5593,11 @@
         <v>19730.5</v>
       </c>
       <c r="M92" s="29">
-        <f>ABS((D92*E92)-L92)</f>
+        <f t="shared" si="4"/>
         <v>504.5</v>
       </c>
       <c r="N92" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B92, $C$2:$C$734, C92, $D$2:$D$734, D92, $E$2:$E$734, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O92" s="41" t="s">
@@ -5627,7 +5605,7 @@
       </c>
       <c r="P92" s="31"/>
     </row>
-    <row r="93" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="32">
         <v>46274.375</v>
       </c>
@@ -5665,11 +5643,11 @@
         <v>19690</v>
       </c>
       <c r="M93" s="29">
-        <f>ABS((D93*E93)-L93)</f>
+        <f t="shared" si="4"/>
         <v>545</v>
       </c>
       <c r="N93" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B93, $C$2:$C$734, C93, $D$2:$D$734, D93, $E$2:$E$734, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O93" s="41" t="s">
@@ -5677,53 +5655,53 @@
       </c>
       <c r="P93" s="31"/>
     </row>
-    <row r="94" spans="1:16" s="70" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="64">
+    <row r="94" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="3">
         <v>46276.375</v>
       </c>
-      <c r="B94" s="65" t="s">
+      <c r="B94" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C94" s="65" t="s">
-        <v>7</v>
-      </c>
-      <c r="D94" s="66">
+      <c r="C94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="4">
         <v>25</v>
       </c>
-      <c r="E94" s="66">
+      <c r="E94" s="4">
         <v>360</v>
       </c>
-      <c r="F94" s="66">
+      <c r="F94" s="4">
         <v>3.956107421</v>
       </c>
-      <c r="G94" s="67" t="s">
+      <c r="G94" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H94" s="68">
+      <c r="H94" s="5">
         <v>346.3</v>
       </c>
-      <c r="I94" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="69" t="s">
+      <c r="I94" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="K94" s="69" t="s">
+      <c r="K94" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="L94" s="69">
+      <c r="L94" s="18">
         <v>8700</v>
       </c>
-      <c r="M94" s="69">
-        <f>ABS((D94*E94)-L94)</f>
+      <c r="M94" s="18">
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
-      <c r="N94" s="70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B94, $C$2:$C$734, C94, $D$2:$D$734, D94, $E$2:$E$734, E94) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" s="25" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N94" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" s="25" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="59">
         <v>46262.375</v>
       </c>
@@ -5761,110 +5739,110 @@
         <v>8420</v>
       </c>
       <c r="M95" s="47">
-        <f>ABS((D95*E95)-L95)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N95" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B95, $C$2:$C$734, C95, $D$2:$D$734, D95, $E$2:$E$734, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P95" s="25" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="96" spans="1:16" s="70" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="64">
+    <row r="96" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="3">
         <v>46267.38958333333</v>
       </c>
-      <c r="B96" s="65" t="s">
+      <c r="B96" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C96" s="65" t="s">
-        <v>7</v>
-      </c>
-      <c r="D96" s="66">
+      <c r="C96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="4">
         <v>100</v>
       </c>
-      <c r="E96" s="66">
+      <c r="E96" s="4">
         <v>344</v>
       </c>
-      <c r="F96" s="66">
+      <c r="F96" s="4">
         <v>4.2517778789999996</v>
       </c>
-      <c r="G96" s="67" t="s">
+      <c r="G96" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H96" s="68">
+      <c r="H96" s="5">
         <v>330.45</v>
       </c>
-      <c r="I96" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="J96" s="69" t="s">
+      <c r="I96" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="K96" s="69" t="s">
+      <c r="K96" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="L96" s="69">
+      <c r="L96" s="18">
         <v>33200</v>
       </c>
-      <c r="M96" s="69">
-        <f>ABS((D96*E96)-L96)</f>
+      <c r="M96" s="18">
+        <f t="shared" si="4"/>
         <v>1200</v>
       </c>
-      <c r="N96" s="70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B96, $C$2:$C$734, C96, $D$2:$D$734, D96, $E$2:$E$734, E96) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" s="70" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="64">
+      <c r="N96" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="3">
         <v>46266.642361111109</v>
       </c>
-      <c r="B97" s="65" t="s">
+      <c r="B97" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C97" s="65" t="s">
-        <v>7</v>
-      </c>
-      <c r="D97" s="66">
+      <c r="C97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" s="4">
         <v>100</v>
       </c>
-      <c r="E97" s="66">
+      <c r="E97" s="4">
         <v>348</v>
       </c>
-      <c r="F97" s="66">
+      <c r="F97" s="4">
         <v>4.2517778789999996</v>
       </c>
-      <c r="G97" s="67" t="s">
+      <c r="G97" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H97" s="68">
+      <c r="H97" s="5">
         <v>330.45</v>
       </c>
-      <c r="I97" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="J97" s="69" t="s">
+      <c r="I97" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J97" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="K97" s="69" t="s">
+      <c r="K97" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="L97" s="69">
+      <c r="L97" s="18">
         <v>33950</v>
       </c>
-      <c r="M97" s="69">
-        <f>ABS((D97*E97)-L97)</f>
+      <c r="M97" s="18">
+        <f t="shared" si="4"/>
         <v>850</v>
       </c>
-      <c r="N97" s="70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B97, $C$2:$C$734, C97, $D$2:$D$734, D97, $E$2:$E$734, E97) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N97" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="32">
         <v>46267.375</v>
       </c>
@@ -5902,15 +5880,15 @@
         <v>5755</v>
       </c>
       <c r="M98" s="29">
-        <f>ABS((D98*E98)-L98)</f>
+        <f t="shared" si="4"/>
         <v>275</v>
       </c>
       <c r="N98" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B98, $C$2:$C$734, C98, $D$2:$D$734, D98, $E$2:$E$734, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="32">
         <v>46267.375</v>
       </c>
@@ -5948,15 +5926,15 @@
         <v>5805</v>
       </c>
       <c r="M99" s="29">
-        <f>ABS((D99*E99)-L99)</f>
+        <f t="shared" si="4"/>
         <v>225</v>
       </c>
       <c r="N99" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B99, $C$2:$C$734, C99, $D$2:$D$734, D99, $E$2:$E$734, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="32">
         <v>46267.425694444442</v>
       </c>
@@ -5994,11 +5972,11 @@
         <v>4120</v>
       </c>
       <c r="M100" s="29">
-        <f>ABS((D100*E100)-L100)</f>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="N100" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B100, $C$2:$C$734, C100, $D$2:$D$734, D100, $E$2:$E$734, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O100" s="30" t="s">
@@ -6006,7 +5984,7 @@
       </c>
       <c r="P100" s="31"/>
     </row>
-    <row r="101" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="32">
         <v>46280.593055555553</v>
       </c>
@@ -6044,11 +6022,11 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M101" s="29">
-        <f>ABS((D101*E101)-L101)</f>
+        <f t="shared" si="4"/>
         <v>188.60000000000014</v>
       </c>
       <c r="N101" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B101, $C$2:$C$734, C101, $D$2:$D$734, D101, $E$2:$E$734, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O101" s="30" t="s">
@@ -6056,7 +6034,7 @@
       </c>
       <c r="P101" s="31"/>
     </row>
-    <row r="102" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3">
         <v>46269.614583333336</v>
       </c>
@@ -6094,18 +6072,18 @@
         <v>8480</v>
       </c>
       <c r="M102" s="27">
-        <f>ABS((D102*E102)-L102)</f>
+        <f t="shared" si="4"/>
         <v>280</v>
       </c>
       <c r="N102" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B102, $C$2:$C$734, C102, $D$2:$D$734, D102, $E$2:$E$734, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3">
         <v>46267.375</v>
       </c>
@@ -6143,16 +6121,16 @@
         <v>9270</v>
       </c>
       <c r="M103" s="18">
-        <f>ABS((D103*E103)-L103)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B103, $C$2:$C$734, C103, $D$2:$D$734, D103, $E$2:$E$734, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P103" s="19"/>
     </row>
-    <row r="104" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="8" t="s">
         <v>62</v>
       </c>
@@ -6184,11 +6162,11 @@
         <v>118</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B104, $C$2:$C$734, C104, $D$2:$D$734, D104, $E$2:$E$734, E104) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -6226,16 +6204,16 @@
         <v>20010</v>
       </c>
       <c r="M105" s="18">
-        <f>ABS((D105*E105)-L105)</f>
+        <f t="shared" ref="M105:M117" si="5">ABS((D105*E105)-L105)</f>
         <v>450</v>
       </c>
       <c r="N105" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B105, $C$2:$C$734, C105, $D$2:$D$734, D105, $E$2:$E$734, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P105"/>
     </row>
-    <row r="106" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3">
         <v>46261.375</v>
       </c>
@@ -6273,16 +6251,16 @@
         <v>14440</v>
       </c>
       <c r="M106" s="18">
-        <f>ABS((D106*E106)-L106)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B106, $C$2:$C$734, C106, $D$2:$D$734, D106, $E$2:$E$734, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O106"/>
     </row>
-    <row r="107" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3">
         <v>46280.57708333333</v>
       </c>
@@ -6320,15 +6298,15 @@
         <v>2899.25</v>
       </c>
       <c r="M107" s="18">
-        <f>ABS((D107*E107)-L107)</f>
+        <f t="shared" si="5"/>
         <v>300.75</v>
       </c>
       <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B107, $C$2:$C$734, C107, $D$2:$D$734, D107, $E$2:$E$734, E107) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="32">
         <v>46335.62777777778</v>
       </c>
@@ -6366,15 +6344,15 @@
         <v>5370</v>
       </c>
       <c r="M108" s="29">
-        <f>ABS((D108*E108)-L108)</f>
+        <f t="shared" si="5"/>
         <v>320</v>
       </c>
       <c r="N108" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B108, $C$2:$C$734, C108, $D$2:$D$734, D108, $E$2:$E$734, E108) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="32">
         <v>46280.375694444447</v>
       </c>
@@ -6412,15 +6390,15 @@
         <v>2610</v>
       </c>
       <c r="M109" s="29">
-        <f>ABS((D109*E109)-L109)</f>
+        <f t="shared" si="5"/>
         <v>235</v>
       </c>
       <c r="N109" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B109, $C$2:$C$734, C109, $D$2:$D$734, D109, $E$2:$E$734, E109) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="3">
         <v>46261.375</v>
       </c>
@@ -6458,16 +6436,16 @@
         <v>34100</v>
       </c>
       <c r="M110" s="18">
-        <f>ABS((D110*E110)-L110)</f>
+        <f t="shared" si="5"/>
         <v>1700</v>
       </c>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B110, $C$2:$C$734, C110, $D$2:$D$734, D110, $E$2:$E$734, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P110" s="10"/>
     </row>
-    <row r="111" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3">
         <v>46267.375</v>
       </c>
@@ -6505,15 +6483,15 @@
         <v>4080</v>
       </c>
       <c r="M111" s="18">
-        <f>ABS((D111*E111)-L111)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B111, $C$2:$C$734, C111, $D$2:$D$734, D111, $E$2:$E$734, E111) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3">
         <v>46280.435416666667</v>
       </c>
@@ -6551,15 +6529,15 @@
         <v>39300</v>
       </c>
       <c r="M112" s="18">
-        <f>ABS((D112*E112)-L112)</f>
+        <f t="shared" si="5"/>
         <v>18350</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B112, $C$2:$C$734, C112, $D$2:$D$734, D112, $E$2:$E$734, E112) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -6597,17 +6575,17 @@
         <v>20260</v>
       </c>
       <c r="M113" s="18">
-        <f>ABS((D113*E113)-L113)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N113" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B113, $C$2:$C$734, C113, $D$2:$D$734, D113, $E$2:$E$734, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O113"/>
       <c r="P113" s="31"/>
     </row>
-    <row r="114" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -6645,18 +6623,18 @@
         <v>15075</v>
       </c>
       <c r="M114" s="18">
-        <f>ABS((D114*E114)-L114)</f>
+        <f t="shared" si="5"/>
         <v>645</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B114, $C$2:$C$734, C114, $D$2:$D$734, D114, $E$2:$E$734, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O114" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="115" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3">
         <v>46261.375</v>
       </c>
@@ -6694,15 +6672,15 @@
         <v>17150</v>
       </c>
       <c r="M115" s="18">
-        <f>ABS((D115*E115)-L115)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B115, $C$2:$C$734, C115, $D$2:$D$734, D115, $E$2:$E$734, E115) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3">
         <v>46274.375</v>
       </c>
@@ -6740,18 +6718,18 @@
         <v>11660</v>
       </c>
       <c r="M116" s="18">
-        <f>ABS((D116*E116)-L116)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B116, $C$2:$C$734, C116, $D$2:$D$734, D116, $E$2:$E$734, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3">
         <v>46281.375</v>
       </c>
@@ -6789,15 +6767,15 @@
         <v>19300</v>
       </c>
       <c r="M117" s="18">
-        <f>ABS((D117*E117)-L117)</f>
+        <f t="shared" si="5"/>
         <v>650</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B117, $C$2:$C$734, C117, $D$2:$D$734, D117, $E$2:$E$734, E117) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6827,11 +6805,11 @@
       </c>
       <c r="J118" s="36"/>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B118, $C$2:$C$734, C118, $D$2:$D$734, D118, $E$2:$E$734, E118) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -6869,18 +6847,18 @@
         <v>73800</v>
       </c>
       <c r="M119" s="18">
-        <f>ABS((D119*E119)-L119)</f>
+        <f t="shared" ref="M119:M125" si="6">ABS((D119*E119)-L119)</f>
         <v>48320</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B119, $C$2:$C$734, C119, $D$2:$D$734, D119, $E$2:$E$734, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O119" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3">
         <v>46280.375694444447</v>
       </c>
@@ -6918,18 +6896,18 @@
         <v>10249</v>
       </c>
       <c r="M120" s="18">
-        <f>ABS((D120*E120)-L120)</f>
+        <f t="shared" si="6"/>
         <v>4451</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B120, $C$2:$C$734, C120, $D$2:$D$734, D120, $E$2:$E$734, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O120" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="121" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="11">
         <v>46243.375</v>
       </c>
@@ -6967,11 +6945,11 @@
         <v>8570</v>
       </c>
       <c r="M121" s="29">
-        <f>ABS((D121*E121)-L121)</f>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B121, $C$2:$C$734, C121, $D$2:$D$734, D121, $E$2:$E$734, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="41" t="s">
@@ -6979,7 +6957,7 @@
       </c>
       <c r="P121" s="10"/>
     </row>
-    <row r="122" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3">
         <v>46275.375</v>
       </c>
@@ -7017,15 +6995,15 @@
         <v>3300</v>
       </c>
       <c r="M122" s="18">
-        <f>ABS((D122*E122)-L122)</f>
+        <f t="shared" si="6"/>
         <v>250</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B122, $C$2:$C$734, C122, $D$2:$D$734, D122, $E$2:$E$734, E122) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3">
         <v>46281.375</v>
       </c>
@@ -7063,18 +7041,18 @@
         <v>16500</v>
       </c>
       <c r="M123" s="18">
-        <f>ABS((D123*E123)-L123)</f>
+        <f t="shared" si="6"/>
         <v>1400</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B123, $C$2:$C$734, C123, $D$2:$D$734, D123, $E$2:$E$734, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O123" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="124" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3">
         <v>46274.375</v>
       </c>
@@ -7112,15 +7090,15 @@
         <v>4852</v>
       </c>
       <c r="M124" s="18">
-        <f>ABS((D124*E124)-L124)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B124, $C$2:$C$734, C124, $D$2:$D$734, D124, $E$2:$E$734, E124) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="3">
         <v>46267.375</v>
       </c>
@@ -7158,16 +7136,16 @@
         <v>3005</v>
       </c>
       <c r="M125" s="18">
-        <f>ABS((D125*E125)-L125)</f>
+        <f t="shared" si="6"/>
         <v>240</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B125, $C$2:$C$734, C125, $D$2:$D$734, D125, $E$2:$E$734, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P125" s="26"/>
     </row>
-    <row r="126" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -7200,7 +7178,7 @@
       <c r="L126" s="18"/>
       <c r="M126" s="18"/>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B126, $C$2:$C$734, C126, $D$2:$D$734, D126, $E$2:$E$734, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="41" t="s">
@@ -7208,7 +7186,7 @@
       </c>
       <c r="P126"/>
     </row>
-    <row r="127" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3">
         <v>46266.375</v>
       </c>
@@ -7250,12 +7228,12 @@
         <v>300</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B127, $C$2:$C$734, C127, $D$2:$D$734, D127, $E$2:$E$734, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P127" s="31"/>
     </row>
-    <row r="128" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="11">
         <v>46253.375</v>
       </c>
@@ -7290,11 +7268,11 @@
         <v>145</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B128, $C$2:$C$734, C128, $D$2:$D$734, D128, $E$2:$E$734, E128) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -7326,11 +7304,11 @@
         <v>117</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B129, $C$2:$C$734, C129, $D$2:$D$734, D129, $E$2:$E$734, E129) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -7372,11 +7350,11 @@
         <v>300</v>
       </c>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B130, $C$2:$C$734, C130, $D$2:$D$734, D130, $E$2:$E$734, E130) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -7418,11 +7396,11 @@
         <v>275</v>
       </c>
       <c r="N131" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B131, $C$2:$C$734, C131, $D$2:$D$734, D131, $E$2:$E$734, E131) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3">
         <v>46335.442361111112</v>
       </c>
@@ -7464,11 +7442,11 @@
         <v>500</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B132, $C$2:$C$734, C132, $D$2:$D$734, D132, $E$2:$E$734, E132) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -7500,7 +7478,7 @@
         <v>118</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B133, $C$2:$C$734, C133, $D$2:$D$734, D133, $E$2:$E$734, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="41" t="s">
@@ -7508,7 +7486,7 @@
       </c>
       <c r="P133"/>
     </row>
-    <row r="134" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="8" t="s">
         <v>62</v>
       </c>
@@ -7538,11 +7516,11 @@
       </c>
       <c r="J134" s="36"/>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B134, $C$2:$C$734, C134, $D$2:$D$734, D134, $E$2:$E$734, E134) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="11">
         <v>46252.645833333336</v>
       </c>
@@ -7572,12 +7550,12 @@
       </c>
       <c r="J135" s="36"/>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B135, $C$2:$C$734, C135, $D$2:$D$734, D135, $E$2:$E$734, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N135:N198" si="7">IF(COUNTIFS( $B$2:$B$734, B135, $C$2:$C$734, C135, $D$2:$D$734, D135, $E$2:$E$734, E135) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O135" s="25"/>
     </row>
-    <row r="136" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3">
         <v>46280.575694444444</v>
       </c>
@@ -7591,7 +7569,7 @@
         <v>5</v>
       </c>
       <c r="E136" s="4">
-        <v>4990</v>
+        <v>4890</v>
       </c>
       <c r="F136" s="4">
         <v>7.2541644280000002</v>
@@ -7615,15 +7593,18 @@
         <v>23450</v>
       </c>
       <c r="M136" s="18">
-        <f>ABS((D136*E136)-L136)</f>
-        <v>1500</v>
+        <f t="shared" ref="M136:M146" si="8">ABS((D136*E136)-L136)</f>
+        <v>1000</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B136, $C$2:$C$734, C136, $D$2:$D$734, D136, $E$2:$E$734, E136) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+      <c r="O136" s="41" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3">
         <v>46281.402777777781</v>
       </c>
@@ -7637,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="E137" s="4">
-        <v>4990</v>
+        <v>4724</v>
       </c>
       <c r="F137" s="4">
         <v>7.2541644280000002</v>
@@ -7661,17 +7642,17 @@
         <v>4410</v>
       </c>
       <c r="M137" s="18">
-        <f>ABS((D137*E137)-L137)</f>
-        <v>580</v>
+        <f t="shared" si="8"/>
+        <v>314</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B137, $C$2:$C$734, C137, $D$2:$D$734, D137, $E$2:$E$734, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="10"/>
       <c r="P137" s="10"/>
     </row>
-    <row r="138" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="35">
         <v>46255</v>
       </c>
@@ -7709,16 +7690,16 @@
         <v>4680</v>
       </c>
       <c r="M138" s="29">
-        <f>ABS((D138*E138)-L138)</f>
+        <f t="shared" si="8"/>
         <v>140</v>
       </c>
       <c r="N138" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B138, $C$2:$C$734, C138, $D$2:$D$734, D138, $E$2:$E$734, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="P138" s="31"/>
     </row>
-    <row r="139" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="32">
         <v>46261.385416666664</v>
       </c>
@@ -7756,17 +7737,17 @@
         <v>4520</v>
       </c>
       <c r="M139" s="29">
-        <f>ABS((D139*E139)-L139)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N139" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B139, $C$2:$C$734, C139, $D$2:$D$734, D139, $E$2:$E$734, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O139" s="10"/>
       <c r="P139" s="10"/>
     </row>
-    <row r="140" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -7804,17 +7785,17 @@
         <v>7200</v>
       </c>
       <c r="M140" s="18">
-        <f>ABS((D140*E140)-L140)</f>
+        <f t="shared" si="8"/>
         <v>250</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B140, $C$2:$C$734, C140, $D$2:$D$734, D140, $E$2:$E$734, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="10"/>
       <c r="P140" s="10"/>
     </row>
-    <row r="141" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -7852,17 +7833,17 @@
         <v>4170</v>
       </c>
       <c r="M141" s="18">
-        <f>ABS((D141*E141)-L141)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N141" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B141, $C$2:$C$734, C141, $D$2:$D$734, D141, $E$2:$E$734, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O141" s="10"/>
       <c r="P141" s="10"/>
     </row>
-    <row r="142" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3">
         <v>46261.615277777775</v>
       </c>
@@ -7900,18 +7881,18 @@
         <v>10814</v>
       </c>
       <c r="M142" s="18">
-        <f>ABS((D142*E142)-L142)</f>
+        <f t="shared" si="8"/>
         <v>501</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B142, $C$2:$C$734, C142, $D$2:$D$734, D142, $E$2:$E$734, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O142" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="143" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="3">
         <v>46276.4</v>
       </c>
@@ -7949,15 +7930,15 @@
         <v>14200</v>
       </c>
       <c r="M143" s="18">
-        <f>ABS((D143*E143)-L143)</f>
+        <f t="shared" si="8"/>
         <v>500</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B143, $C$2:$C$734, C143, $D$2:$D$734, D143, $E$2:$E$734, E143) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="11">
         <v>46243.375</v>
       </c>
@@ -7995,16 +7976,16 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M144" s="29">
-        <f>ABS((D144*E144)-L144)</f>
+        <f t="shared" si="8"/>
         <v>710.99999999999636</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B144, $C$2:$C$734, C144, $D$2:$D$734, D144, $E$2:$E$734, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P144"/>
     </row>
-    <row r="145" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -8042,18 +8023,18 @@
         <v>73800</v>
       </c>
       <c r="M145" s="18">
-        <f>ABS((D145*E145)-L145)</f>
+        <f t="shared" si="8"/>
         <v>47900</v>
       </c>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B145, $C$2:$C$734, C145, $D$2:$D$734, D145, $E$2:$E$734, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O145" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="146" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="3">
         <v>46262.375</v>
       </c>
@@ -8091,16 +8072,16 @@
         <v>10410</v>
       </c>
       <c r="M146" s="18">
-        <f>ABS((D146*E146)-L146)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B146, $C$2:$C$734, C146, $D$2:$D$734, D146, $E$2:$E$734, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="31"/>
     </row>
-    <row r="147" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -8130,12 +8111,12 @@
       </c>
       <c r="J147" s="36"/>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B147, $C$2:$C$734, C147, $D$2:$D$734, D147, $E$2:$E$734, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O147" s="31"/>
     </row>
-    <row r="148" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="3">
         <v>46266.375</v>
       </c>
@@ -8173,18 +8154,18 @@
         <v>25300</v>
       </c>
       <c r="M148" s="18">
-        <f>ABS((D148*E148)-L148)</f>
+        <f t="shared" ref="M148:M159" si="9">ABS((D148*E148)-L148)</f>
         <v>650</v>
       </c>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B148, $C$2:$C$734, C148, $D$2:$D$734, D148, $E$2:$E$734, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -8222,18 +8203,18 @@
         <v>12480</v>
       </c>
       <c r="M149" s="18">
-        <f>ABS((D149*E149)-L149)</f>
+        <f t="shared" si="9"/>
         <v>495</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B149, $C$2:$C$734, C149, $D$2:$D$734, D149, $E$2:$E$734, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="32">
         <v>46260.556944444441</v>
       </c>
@@ -8271,15 +8252,15 @@
         <v>6105</v>
       </c>
       <c r="M150" s="29">
-        <f>ABS((D150*E150)-L150)</f>
+        <f t="shared" si="9"/>
         <v>150</v>
       </c>
       <c r="N150" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B150, $C$2:$C$734, C150, $D$2:$D$734, D150, $E$2:$E$734, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="151" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="32">
         <v>46261.375</v>
       </c>
@@ -8317,15 +8298,15 @@
         <v>6005</v>
       </c>
       <c r="M151" s="29">
-        <f>ABS((D151*E151)-L151)</f>
+        <f t="shared" si="9"/>
         <v>250</v>
       </c>
       <c r="N151" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B151, $C$2:$C$734, C151, $D$2:$D$734, D151, $E$2:$E$734, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="152" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="45">
         <v>46273.385416666664</v>
       </c>
@@ -8363,11 +8344,11 @@
         <v>16580</v>
       </c>
       <c r="M152" s="47">
-        <f>ABS((D152*E152)-L152)</f>
+        <f t="shared" si="9"/>
         <v>750</v>
       </c>
       <c r="N152" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B152, $C$2:$C$734, C152, $D$2:$D$734, D152, $E$2:$E$734, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O152" s="25"/>
@@ -8375,7 +8356,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="153" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="3">
         <v>46269.411111111112</v>
       </c>
@@ -8413,17 +8394,17 @@
         <v>18140</v>
       </c>
       <c r="M153" s="27">
-        <f>ABS((D153*E153)-L153)</f>
+        <f t="shared" si="9"/>
         <v>650</v>
       </c>
       <c r="N153" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B153, $C$2:$C$734, C153, $D$2:$D$734, D153, $E$2:$E$734, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="10"/>
       <c r="P153" s="10"/>
     </row>
-    <row r="154" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3">
         <v>46265.474999999999</v>
       </c>
@@ -8461,15 +8442,15 @@
         <v>3810</v>
       </c>
       <c r="M154" s="18">
-        <f>ABS((D154*E154)-L154)</f>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N154" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B154, $C$2:$C$734, C154, $D$2:$D$734, D154, $E$2:$E$734, E154) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="155" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -8507,18 +8488,18 @@
         <v>18800</v>
       </c>
       <c r="M155" s="18">
-        <f>ABS((D155*E155)-L155)</f>
+        <f t="shared" si="9"/>
         <v>500</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B155, $C$2:$C$734, C155, $D$2:$D$734, D155, $E$2:$E$734, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O155" s="42" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="156" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="32">
         <v>46265.375694444447</v>
       </c>
@@ -8556,15 +8537,15 @@
         <v>7578</v>
       </c>
       <c r="M156" s="29">
-        <f>ABS((D156*E156)-L156)</f>
+        <f t="shared" si="9"/>
         <v>294</v>
       </c>
       <c r="N156" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B156, $C$2:$C$734, C156, $D$2:$D$734, D156, $E$2:$E$734, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="157" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="32">
         <v>46266.375694444447</v>
       </c>
@@ -8602,15 +8583,15 @@
         <v>7578</v>
       </c>
       <c r="M157" s="29">
-        <f>ABS((D157*E157)-L157)</f>
+        <f t="shared" si="9"/>
         <v>294</v>
       </c>
       <c r="N157" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B157, $C$2:$C$734, C157, $D$2:$D$734, D157, $E$2:$E$734, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="158" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="32">
         <v>46267.424305555556</v>
       </c>
@@ -8648,15 +8629,15 @@
         <v>4968</v>
       </c>
       <c r="M158" s="29">
-        <f>ABS((D158*E158)-L158)</f>
+        <f t="shared" si="9"/>
         <v>280</v>
       </c>
       <c r="N158" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B158, $C$2:$C$734, C158, $D$2:$D$734, D158, $E$2:$E$734, E158) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -8694,11 +8675,11 @@
         <v>25780</v>
       </c>
       <c r="M159" s="18">
-        <f>ABS((D159*E159)-L159)</f>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N159" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B159, $C$2:$C$734, C159, $D$2:$D$734, D159, $E$2:$E$734, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="41" t="s">
@@ -8706,7 +8687,7 @@
       </c>
       <c r="P159"/>
     </row>
-    <row r="160" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -8736,11 +8717,11 @@
       </c>
       <c r="J160" s="36"/>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B160, $C$2:$C$734, C160, $D$2:$D$734, D160, $E$2:$E$734, E160) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="161" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="3">
         <v>46269.375</v>
       </c>
@@ -8782,11 +8763,11 @@
         <v>250</v>
       </c>
       <c r="N161" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B161, $C$2:$C$734, C161, $D$2:$D$734, D161, $E$2:$E$734, E161) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="162" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3">
         <v>46261.375</v>
       </c>
@@ -8828,11 +8809,11 @@
         <v>300</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B162, $C$2:$C$734, C162, $D$2:$D$734, D162, $E$2:$E$734, E162) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="3">
         <v>46265.390277777777</v>
       </c>
@@ -8874,13 +8855,13 @@
         <v>650</v>
       </c>
       <c r="N163" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B163, $C$2:$C$734, C163, $D$2:$D$734, D163, $E$2:$E$734, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O163"/>
       <c r="P163"/>
     </row>
-    <row r="164" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -8912,11 +8893,11 @@
         <v>117</v>
       </c>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B164, $C$2:$C$734, C164, $D$2:$D$734, D164, $E$2:$E$734, E164) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -8954,15 +8935,15 @@
         <v>12510</v>
       </c>
       <c r="M165" s="18">
-        <f>ABS((D165*E165)-L165)</f>
+        <f t="shared" ref="M165:M170" si="10">ABS((D165*E165)-L165)</f>
         <v>290</v>
       </c>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B165, $C$2:$C$734, C165, $D$2:$D$734, D165, $E$2:$E$734, E165) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="166" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="3">
         <v>46276.390277777777</v>
       </c>
@@ -9000,17 +8981,17 @@
         <v>14400</v>
       </c>
       <c r="M166" s="18">
-        <f>ABS((D166*E166)-L166)</f>
+        <f t="shared" si="10"/>
         <v>500</v>
       </c>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B166, $C$2:$C$734, C166, $D$2:$D$734, D166, $E$2:$E$734, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O166" s="10"/>
       <c r="P166" s="10"/>
     </row>
-    <row r="167" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="32">
         <v>46258.443055555559</v>
       </c>
@@ -9048,17 +9029,17 @@
         <v>11175</v>
       </c>
       <c r="M167" s="29">
-        <f>ABS((D167*E167)-L167)</f>
+        <f t="shared" si="10"/>
         <v>300</v>
       </c>
       <c r="N167" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B167, $C$2:$C$734, C167, $D$2:$D$734, D167, $E$2:$E$734, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O167" s="31"/>
       <c r="P167" s="31"/>
     </row>
-    <row r="168" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="32">
         <v>46259.375</v>
       </c>
@@ -9096,17 +9077,17 @@
         <v>4402</v>
       </c>
       <c r="M168" s="29">
-        <f>ABS((D168*E168)-L168)</f>
+        <f t="shared" si="10"/>
         <v>188</v>
       </c>
       <c r="N168" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B168, $C$2:$C$734, C168, $D$2:$D$734, D168, $E$2:$E$734, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O168" s="31"/>
       <c r="P168" s="31"/>
     </row>
-    <row r="169" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="32">
         <v>46272.451388888891</v>
       </c>
@@ -9144,17 +9125,17 @@
         <v>8820</v>
       </c>
       <c r="M169" s="29">
-        <f>ABS((D169*E169)-L169)</f>
+        <f t="shared" si="10"/>
         <v>650</v>
       </c>
       <c r="N169" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B169, $C$2:$C$734, C169, $D$2:$D$734, D169, $E$2:$E$734, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O169" s="31"/>
       <c r="P169" s="31"/>
     </row>
-    <row r="170" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="32">
         <v>46272.390972222223</v>
       </c>
@@ -9192,17 +9173,17 @@
         <v>36946</v>
       </c>
       <c r="M170" s="29">
-        <f>ABS((D170*E170)-L170)</f>
+        <f t="shared" si="10"/>
         <v>934</v>
       </c>
       <c r="N170" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B170, $C$2:$C$734, C170, $D$2:$D$734, D170, $E$2:$E$734, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O170" s="31"/>
       <c r="P170" s="31"/>
     </row>
-    <row r="171" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -9235,13 +9216,13 @@
       <c r="L171" s="18"/>
       <c r="M171" s="18"/>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B171, $C$2:$C$734, C171, $D$2:$D$734, D171, $E$2:$E$734, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O171" s="10"/>
       <c r="P171" s="10"/>
     </row>
-    <row r="172" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="3">
         <v>46274.375</v>
       </c>
@@ -9283,13 +9264,13 @@
         <v>250</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B172, $C$2:$C$734, C172, $D$2:$D$734, D172, $E$2:$E$734, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O172" s="10"/>
       <c r="P172" s="10"/>
     </row>
-    <row r="173" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="32">
         <v>46265.375694444447</v>
       </c>
@@ -9331,12 +9312,14 @@
         <v>300</v>
       </c>
       <c r="N173" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B173, $C$2:$C$734, C173, $D$2:$D$734, D173, $E$2:$E$734, E173) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O173" s="31"/>
-    </row>
-    <row r="174" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+      <c r="O173" s="41" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="43">
         <v>46243.505555555559</v>
       </c>
@@ -9378,12 +9361,14 @@
         <v>253</v>
       </c>
       <c r="N174" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B174, $C$2:$C$734, C174, $D$2:$D$734, D174, $E$2:$E$734, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
-      <c r="O174" s="31"/>
-    </row>
-    <row r="175" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O174" s="41" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="32">
         <v>46280.588194444441</v>
       </c>
@@ -9425,13 +9410,15 @@
         <v>355.5</v>
       </c>
       <c r="N175" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B175, $C$2:$C$734, C175, $D$2:$D$734, D175, $E$2:$E$734, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
-      <c r="O175" s="31"/>
+      <c r="O175" s="41" t="s">
+        <v>246</v>
+      </c>
       <c r="P175" s="31"/>
     </row>
-    <row r="176" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="46" t="s">
         <v>62</v>
       </c>
@@ -9466,7 +9453,7 @@
       <c r="L176" s="47"/>
       <c r="M176" s="47"/>
       <c r="N176" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B176, $C$2:$C$734, C176, $D$2:$D$734, D176, $E$2:$E$734, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O176" s="25"/>
@@ -9474,7 +9461,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="177" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="11">
         <v>46243.375</v>
       </c>
@@ -9516,12 +9503,12 @@
         <v>300</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B177, $C$2:$C$734, C177, $D$2:$D$734, D177, $E$2:$E$734, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P177" s="26"/>
     </row>
-    <row r="178" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="8" t="s">
         <v>62</v>
       </c>
@@ -9551,11 +9538,11 @@
       </c>
       <c r="J178" s="36"/>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B178, $C$2:$C$734, C178, $D$2:$D$734, D178, $E$2:$E$734, E178) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -9597,7 +9584,7 @@
         <v>47480</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B179, $C$2:$C$734, C179, $D$2:$D$734, D179, $E$2:$E$734, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9629,20 +9616,20 @@
       <c r="I180" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J180" s="71" t="s">
+      <c r="J180" s="52" t="s">
         <v>41</v>
       </c>
       <c r="K180" s="17"/>
       <c r="L180" s="17"/>
       <c r="M180" s="17"/>
       <c r="N180" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B180, $C$2:$C$734, C180, $D$2:$D$734, D180, $E$2:$E$734, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O180"/>
       <c r="P180"/>
     </row>
-    <row r="181" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -9684,11 +9671,11 @@
         <v>340</v>
       </c>
       <c r="N181" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B181, $C$2:$C$734, C181, $D$2:$D$734, D181, $E$2:$E$734, E181) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -9730,7 +9717,7 @@
         <v>880</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B182, $C$2:$C$734, C182, $D$2:$D$734, D182, $E$2:$E$734, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O182" s="41" t="s">
@@ -9738,7 +9725,7 @@
       </c>
       <c r="P182" s="10"/>
     </row>
-    <row r="183" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="3">
         <v>46276.375</v>
       </c>
@@ -9780,13 +9767,13 @@
         <v>816</v>
       </c>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B183, $C$2:$C$734, C183, $D$2:$D$734, D183, $E$2:$E$734, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="10"/>
       <c r="P183" s="10"/>
     </row>
-    <row r="184" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9818,14 +9805,14 @@
         <v>118</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B184, $C$2:$C$734, C184, $D$2:$D$734, D184, $E$2:$E$734, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O184" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="185" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="3">
         <v>46281.37777777778</v>
       </c>
@@ -9867,11 +9854,11 @@
         <v>810</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B185, $C$2:$C$734, C185, $D$2:$D$734, D185, $E$2:$E$734, E185) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="186" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="3">
         <v>46262.463194444441</v>
       </c>
@@ -9913,11 +9900,11 @@
         <v>300</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B186, $C$2:$C$734, C186, $D$2:$D$734, D186, $E$2:$E$734, E186) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="11">
         <v>46252.6875</v>
       </c>
@@ -9949,11 +9936,11 @@
         <v>118</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B187, $C$2:$C$734, C187, $D$2:$D$734, D187, $E$2:$E$734, E187) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="8" t="s">
         <v>62</v>
       </c>
@@ -9985,11 +9972,11 @@
         <v>117</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B188, $C$2:$C$734, C188, $D$2:$D$734, D188, $E$2:$E$734, E188) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -10021,11 +10008,11 @@
         <v>117</v>
       </c>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B189, $C$2:$C$734, C189, $D$2:$D$734, D189, $E$2:$E$734, E189) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="3">
         <v>46266.375</v>
       </c>
@@ -10067,11 +10054,11 @@
         <v>360</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B190, $C$2:$C$734, C190, $D$2:$D$734, D190, $E$2:$E$734, E190) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -10113,11 +10100,11 @@
         <v>300</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B191, $C$2:$C$734, C191, $D$2:$D$734, D191, $E$2:$E$734, E191) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -10149,11 +10136,11 @@
         <v>118</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B192, $C$2:$C$734, C192, $D$2:$D$734, D192, $E$2:$E$734, E192) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="193" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="32">
         <v>46258.443749999999</v>
       </c>
@@ -10195,13 +10182,13 @@
         <v>527.5</v>
       </c>
       <c r="N193" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B193, $C$2:$C$734, C193, $D$2:$D$734, D193, $E$2:$E$734, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O193" s="31"/>
       <c r="P193" s="31"/>
     </row>
-    <row r="194" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="43">
         <v>46253.4</v>
       </c>
@@ -10238,11 +10225,11 @@
       <c r="L194" s="29"/>
       <c r="M194" s="29"/>
       <c r="N194" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B194, $C$2:$C$734, C194, $D$2:$D$734, D194, $E$2:$E$734, E194) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="195" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="3">
         <v>46276.388194444444</v>
       </c>
@@ -10284,11 +10271,11 @@
         <v>450</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B195, $C$2:$C$734, C195, $D$2:$D$734, D195, $E$2:$E$734, E195) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="196" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="3">
         <v>46262.375</v>
       </c>
@@ -10330,11 +10317,11 @@
         <v>320</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B196, $C$2:$C$734, C196, $D$2:$D$734, D196, $E$2:$E$734, E196) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="3">
         <v>46265.486111111109</v>
       </c>
@@ -10376,11 +10363,11 @@
         <v>448</v>
       </c>
       <c r="N197" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B197, $C$2:$C$734, C197, $D$2:$D$734, D197, $E$2:$E$734, E197) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="198" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="3">
         <v>46262.375</v>
       </c>
@@ -10422,11 +10409,11 @@
         <v>300</v>
       </c>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B198, $C$2:$C$734, C198, $D$2:$D$734, D198, $E$2:$E$734, E198) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="199" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="3">
         <v>46274.375</v>
       </c>
@@ -10468,13 +10455,13 @@
         <v>651</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B199, $C$2:$C$734, C199, $D$2:$D$734, D199, $E$2:$E$734, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N199:N262" si="11">IF(COUNTIFS( $B$2:$B$734, B199, $C$2:$C$734, C199, $D$2:$D$734, D199, $E$2:$E$734, E199) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O199" s="10"/>
       <c r="P199" s="10"/>
     </row>
-    <row r="200" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="9" t="s">
         <v>62</v>
       </c>
@@ -10504,11 +10491,11 @@
       </c>
       <c r="J200" s="36"/>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B200, $C$2:$C$734, C200, $D$2:$D$734, D200, $E$2:$E$734, E200) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="201" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="3">
         <v>46260.425694444442</v>
       </c>
@@ -10550,12 +10537,12 @@
         <v>1000</v>
       </c>
       <c r="N201" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B201, $C$2:$C$734, C201, $D$2:$D$734, D201, $E$2:$E$734, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P201" s="31"/>
     </row>
-    <row r="202" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="3">
         <v>46335.421527777777</v>
       </c>
@@ -10597,14 +10584,14 @@
         <v>800</v>
       </c>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B202, $C$2:$C$734, C202, $D$2:$D$734, D202, $E$2:$E$734, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O202" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="203" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -10646,11 +10633,11 @@
         <v>260</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B203, $C$2:$C$734, C203, $D$2:$D$734, D203, $E$2:$E$734, E203) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="204" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -10687,11 +10674,11 @@
       <c r="L204" s="17"/>
       <c r="M204" s="17"/>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B204, $C$2:$C$734, C204, $D$2:$D$734, D204, $E$2:$E$734, E204) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="205" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10721,12 +10708,12 @@
       </c>
       <c r="J205" s="36"/>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B205, $C$2:$C$734, C205, $D$2:$D$734, D205, $E$2:$E$734, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O205" s="31"/>
     </row>
-    <row r="206" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="8" t="s">
         <v>62</v>
       </c>
@@ -10756,11 +10743,11 @@
       </c>
       <c r="J206" s="36"/>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B206, $C$2:$C$734, C206, $D$2:$D$734, D206, $E$2:$E$734, E206) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="207" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="8" t="s">
         <v>62</v>
       </c>
@@ -10792,11 +10779,11 @@
         <v>117</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B207, $C$2:$C$734, C207, $D$2:$D$734, D207, $E$2:$E$734, E207) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="208" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10828,11 +10815,11 @@
         <v>55</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B208, $C$2:$C$734, C208, $D$2:$D$734, D208, $E$2:$E$734, E208) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="209" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="3">
         <v>46266.375</v>
       </c>
@@ -10874,7 +10861,7 @@
         <v>300</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B209, $C$2:$C$734, C209, $D$2:$D$734, D209, $E$2:$E$734, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O209" s="41" t="s">
@@ -10882,7 +10869,7 @@
       </c>
       <c r="P209" s="31"/>
     </row>
-    <row r="210" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="8" t="s">
         <v>62</v>
       </c>
@@ -10914,11 +10901,11 @@
         <v>118</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B210, $C$2:$C$734, C210, $D$2:$D$734, D210, $E$2:$E$734, E210) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="211" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="8" t="s">
         <v>62</v>
       </c>
@@ -10950,11 +10937,11 @@
         <v>55</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B211, $C$2:$C$734, C211, $D$2:$D$734, D211, $E$2:$E$734, E211) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="212" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="11">
         <v>46253.375</v>
       </c>
@@ -10989,11 +10976,11 @@
         <v>144</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B212, $C$2:$C$734, C212, $D$2:$D$734, D212, $E$2:$E$734, E212) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="213" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="8" t="s">
         <v>62</v>
       </c>
@@ -11025,11 +11012,11 @@
         <v>118</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B213, $C$2:$C$734, C213, $D$2:$D$734, D213, $E$2:$E$734, E213) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="214" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="8" t="s">
         <v>62</v>
       </c>
@@ -11061,11 +11048,11 @@
         <v>196</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B214, $C$2:$C$734, C214, $D$2:$D$734, D214, $E$2:$E$734, E214) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="215" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="11">
         <v>46252.6875</v>
       </c>
@@ -11097,11 +11084,11 @@
         <v>117</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B215, $C$2:$C$734, C215, $D$2:$D$734, D215, $E$2:$E$734, E215) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="216" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="11">
         <v>46252.6875</v>
       </c>
@@ -11133,11 +11120,11 @@
         <v>154</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B216, $C$2:$C$734, C216, $D$2:$D$734, D216, $E$2:$E$734, E216) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="217" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -11179,11 +11166,11 @@
         <v>940</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B217, $C$2:$C$734, C217, $D$2:$D$734, D217, $E$2:$E$734, E217) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="218" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="8" t="s">
         <v>62</v>
       </c>
@@ -11218,12 +11205,12 @@
       <c r="L218" s="18"/>
       <c r="M218" s="18"/>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B218, $C$2:$C$734, C218, $D$2:$D$734, D218, $E$2:$E$734, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P218" s="10"/>
     </row>
-    <row r="219" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -11265,11 +11252,11 @@
         <v>400</v>
       </c>
       <c r="N219" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B219, $C$2:$C$734, C219, $D$2:$D$734, D219, $E$2:$E$734, E219) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="220" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="3">
         <v>46265.460416666669</v>
       </c>
@@ -11311,12 +11298,12 @@
         <v>650</v>
       </c>
       <c r="N220" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B220, $C$2:$C$734, C220, $D$2:$D$734, D220, $E$2:$E$734, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P220" s="31"/>
     </row>
-    <row r="221" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="8" t="s">
         <v>62</v>
       </c>
@@ -11346,11 +11333,11 @@
       </c>
       <c r="J221" s="36"/>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B221, $C$2:$C$734, C221, $D$2:$D$734, D221, $E$2:$E$734, E221) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="222" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="8" t="s">
         <v>62</v>
       </c>
@@ -11382,12 +11369,12 @@
         <v>118</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B222, $C$2:$C$734, C222, $D$2:$D$734, D222, $E$2:$E$734, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O222" s="31"/>
     </row>
-    <row r="223" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="8" t="s">
         <v>62</v>
       </c>
@@ -11417,11 +11404,11 @@
       </c>
       <c r="J223" s="36"/>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B223, $C$2:$C$734, C223, $D$2:$D$734, D223, $E$2:$E$734, E223) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="224" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="8" t="s">
         <v>62</v>
       </c>
@@ -11453,11 +11440,11 @@
         <v>118</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B224, $C$2:$C$734, C224, $D$2:$D$734, D224, $E$2:$E$734, E224) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="225" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="225" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="3">
         <v>46266.509722222225</v>
       </c>
@@ -11499,11 +11486,11 @@
         <v>300</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B225, $C$2:$C$734, C225, $D$2:$D$734, D225, $E$2:$E$734, E225) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="226" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="8" t="s">
         <v>62</v>
       </c>
@@ -11533,11 +11520,11 @@
       </c>
       <c r="J226" s="36"/>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B226, $C$2:$C$734, C226, $D$2:$D$734, D226, $E$2:$E$734, E226) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="227" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="11">
         <v>46252.6875</v>
       </c>
@@ -11572,13 +11559,13 @@
       <c r="L227" s="18"/>
       <c r="M227" s="18"/>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B227, $C$2:$C$734, C227, $D$2:$D$734, D227, $E$2:$E$734, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O227" s="10"/>
       <c r="P227" s="10"/>
     </row>
-    <row r="228" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -11620,12 +11607,12 @@
         <v>250</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B228, $C$2:$C$734, C228, $D$2:$D$734, D228, $E$2:$E$734, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P228" s="31"/>
     </row>
-    <row r="229" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -11660,11 +11647,11 @@
         <v>146</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B229, $C$2:$C$734, C229, $D$2:$D$734, D229, $E$2:$E$734, E229) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="230" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -11706,14 +11693,14 @@
         <v>500</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B230, $C$2:$C$734, C230, $D$2:$D$734, D230, $E$2:$E$734, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O230" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="231" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -11743,12 +11730,12 @@
       </c>
       <c r="J231" s="36"/>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B231, $C$2:$C$734, C231, $D$2:$D$734, D231, $E$2:$E$734, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P231" s="31"/>
     </row>
-    <row r="232" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="3">
         <v>46274.414583333331</v>
       </c>
@@ -11790,14 +11777,14 @@
         <v>646</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B232, $C$2:$C$734, C232, $D$2:$D$734, D232, $E$2:$E$734, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O232" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="233" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="3">
         <v>46276.375</v>
       </c>
@@ -11839,11 +11826,11 @@
         <v>450</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B233, $C$2:$C$734, C233, $D$2:$D$734, D233, $E$2:$E$734, E233) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="8" t="s">
         <v>62</v>
       </c>
@@ -11875,11 +11862,11 @@
         <v>117</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B234, $C$2:$C$734, C234, $D$2:$D$734, D234, $E$2:$E$734, E234) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="8" t="s">
         <v>62</v>
       </c>
@@ -11911,11 +11898,11 @@
         <v>117</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B235, $C$2:$C$734, C235, $D$2:$D$734, D235, $E$2:$E$734, E235) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="236" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="8" t="s">
         <v>62</v>
       </c>
@@ -11947,11 +11934,11 @@
         <v>118</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B236, $C$2:$C$734, C236, $D$2:$D$734, D236, $E$2:$E$734, E236) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="237" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="3">
         <v>46262.375</v>
       </c>
@@ -11993,12 +11980,12 @@
         <v>370</v>
       </c>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B237, $C$2:$C$734, C237, $D$2:$D$734, D237, $E$2:$E$734, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P237" s="31"/>
     </row>
-    <row r="238" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="11">
         <v>46252.6875</v>
       </c>
@@ -12030,11 +12017,11 @@
         <v>117</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B238, $C$2:$C$734, C238, $D$2:$D$734, D238, $E$2:$E$734, E238) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="239" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="8" t="s">
         <v>62</v>
       </c>
@@ -12064,11 +12051,11 @@
       </c>
       <c r="J239" s="36"/>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B239, $C$2:$C$734, C239, $D$2:$D$734, D239, $E$2:$E$734, E239) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="240" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="8" t="s">
         <v>62</v>
       </c>
@@ -12100,12 +12087,12 @@
         <v>117</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B240, $C$2:$C$734, C240, $D$2:$D$734, D240, $E$2:$E$734, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P240" s="31"/>
     </row>
-    <row r="241" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="8" t="s">
         <v>62</v>
       </c>
@@ -12137,11 +12124,11 @@
         <v>118</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B241, $C$2:$C$734, C241, $D$2:$D$734, D241, $E$2:$E$734, E241) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="242" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="3">
         <v>46260.375</v>
       </c>
@@ -12179,15 +12166,15 @@
         <v>17920</v>
       </c>
       <c r="M242" s="18">
-        <f t="shared" ref="M242:M247" si="0">ABS((D242*E242)-L242)</f>
+        <f t="shared" ref="M242:M247" si="12">ABS((D242*E242)-L242)</f>
         <v>800</v>
       </c>
       <c r="N242" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B242, $C$2:$C$734, C242, $D$2:$D$734, D242, $E$2:$E$734, E242) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="243" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="3">
         <v>46260.375</v>
       </c>
@@ -12225,16 +12212,16 @@
         <v>9320</v>
       </c>
       <c r="M243" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>650</v>
       </c>
       <c r="N243" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B243, $C$2:$C$734, C243, $D$2:$D$734, D243, $E$2:$E$734, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P243" s="31"/>
     </row>
-    <row r="244" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="3">
         <v>46268.375</v>
       </c>
@@ -12272,15 +12259,15 @@
         <v>25800</v>
       </c>
       <c r="M244" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>1800</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B244, $C$2:$C$734, C244, $D$2:$D$734, D244, $E$2:$E$734, E244) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="245" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="3">
         <v>46259.375</v>
       </c>
@@ -12318,16 +12305,16 @@
         <v>8800</v>
       </c>
       <c r="M245" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>650</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B245, $C$2:$C$734, C245, $D$2:$D$734, D245, $E$2:$E$734, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="31"/>
     </row>
-    <row r="246" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -12365,15 +12352,15 @@
         <v>2260</v>
       </c>
       <c r="M246" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>250</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B246, $C$2:$C$734, C246, $D$2:$D$734, D246, $E$2:$E$734, E246) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="247" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="3">
         <v>46262.375</v>
       </c>
@@ -12411,15 +12398,15 @@
         <v>13300</v>
       </c>
       <c r="M247" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>300</v>
       </c>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B247, $C$2:$C$734, C247, $D$2:$D$734, D247, $E$2:$E$734, E247) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="248" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="8" t="s">
         <v>62</v>
       </c>
@@ -12449,11 +12436,11 @@
       </c>
       <c r="J248" s="36"/>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B248, $C$2:$C$734, C248, $D$2:$D$734, D248, $E$2:$E$734, E248) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="249" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="8" t="s">
         <v>62</v>
       </c>
@@ -12483,11 +12470,11 @@
       </c>
       <c r="J249" s="36"/>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B249, $C$2:$C$734, C249, $D$2:$D$734, D249, $E$2:$E$734, E249) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="250" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="8" t="s">
         <v>62</v>
       </c>
@@ -12519,11 +12506,11 @@
         <v>117</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B250, $C$2:$C$734, C250, $D$2:$D$734, D250, $E$2:$E$734, E250) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="251" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="8" t="s">
         <v>62</v>
       </c>
@@ -12553,11 +12540,11 @@
       </c>
       <c r="J251" s="36"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B251, $C$2:$C$734, C251, $D$2:$D$734, D251, $E$2:$E$734, E251) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="252" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="11">
         <v>46252.6875</v>
       </c>
@@ -12589,12 +12576,12 @@
         <v>118</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B252, $C$2:$C$734, C252, $D$2:$D$734, D252, $E$2:$E$734, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O252" s="31"/>
     </row>
-    <row r="253" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="8" t="s">
         <v>62</v>
       </c>
@@ -12624,11 +12611,11 @@
       </c>
       <c r="J253" s="36"/>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B253, $C$2:$C$734, C253, $D$2:$D$734, D253, $E$2:$E$734, E253) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="20">
         <v>46255</v>
       </c>
@@ -12670,11 +12657,11 @@
         <v>300</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B254, $C$2:$C$734, C254, $D$2:$D$734, D254, $E$2:$E$734, E254) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="255" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12704,11 +12691,11 @@
       </c>
       <c r="J255" s="36"/>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B255, $C$2:$C$734, C255, $D$2:$D$734, D255, $E$2:$E$734, E255) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="256" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="8" t="s">
         <v>62</v>
       </c>
@@ -12740,11 +12727,11 @@
         <v>118</v>
       </c>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B256, $C$2:$C$734, C256, $D$2:$D$734, D256, $E$2:$E$734, E256) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="257" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="3">
         <v>46269.643055555556</v>
       </c>
@@ -12786,11 +12773,11 @@
         <v>268</v>
       </c>
       <c r="N257" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B257, $C$2:$C$734, C257, $D$2:$D$734, D257, $E$2:$E$734, E257) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="258" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="3">
         <v>46261.375</v>
       </c>
@@ -12832,11 +12819,11 @@
         <v>260</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B258, $C$2:$C$734, C258, $D$2:$D$734, D258, $E$2:$E$734, E258) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="259" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="8" t="s">
         <v>62</v>
       </c>
@@ -12868,11 +12855,11 @@
         <v>118</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B259, $C$2:$C$734, C259, $D$2:$D$734, D259, $E$2:$E$734, E259) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="260" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="8" t="s">
         <v>62</v>
       </c>
@@ -12902,11 +12889,11 @@
       </c>
       <c r="J260" s="36"/>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B260, $C$2:$C$734, C260, $D$2:$D$734, D260, $E$2:$E$734, E260) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="261" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="3">
         <v>46260.634027777778</v>
       </c>
@@ -12948,11 +12935,11 @@
         <v>480</v>
       </c>
       <c r="N261" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B261, $C$2:$C$734, C261, $D$2:$D$734, D261, $E$2:$E$734, E261) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="262" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="8" t="s">
         <v>62</v>
       </c>
@@ -12982,11 +12969,11 @@
       </c>
       <c r="J262" s="36"/>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B262, $C$2:$C$734, C262, $D$2:$D$734, D262, $E$2:$E$734, E262) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="263" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="8" t="s">
         <v>62</v>
       </c>
@@ -13016,11 +13003,11 @@
       </c>
       <c r="J263" s="36"/>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B263, $C$2:$C$734, C263, $D$2:$D$734, D263, $E$2:$E$734, E263) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="264" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="N263:N295" si="13">IF(COUNTIFS( $B$2:$B$734, B263, $C$2:$C$734, C263, $D$2:$D$734, D263, $E$2:$E$734, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="3">
         <v>46260.375</v>
       </c>
@@ -13062,11 +13049,11 @@
         <v>300</v>
       </c>
       <c r="N264" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B264, $C$2:$C$734, C264, $D$2:$D$734, D264, $E$2:$E$734, E264) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="265" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="8" t="s">
         <v>62</v>
       </c>
@@ -13101,13 +13088,13 @@
       <c r="L265" s="18"/>
       <c r="M265" s="18"/>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B265, $C$2:$C$734, C265, $D$2:$D$734, D265, $E$2:$E$734, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O265" s="10"/>
       <c r="P265" s="10"/>
     </row>
-    <row r="266" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="8" t="s">
         <v>62</v>
       </c>
@@ -13140,13 +13127,13 @@
       <c r="L266" s="18"/>
       <c r="M266" s="18"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B266, $C$2:$C$734, C266, $D$2:$D$734, D266, $E$2:$E$734, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O266" s="10"/>
       <c r="P266" s="10"/>
     </row>
-    <row r="267" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="8" t="s">
         <v>62</v>
       </c>
@@ -13176,12 +13163,12 @@
       </c>
       <c r="J267" s="36"/>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B267, $C$2:$C$734, C267, $D$2:$D$734, D267, $E$2:$E$734, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="P267" s="31"/>
     </row>
-    <row r="268" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="3">
         <v>46260.554861111108</v>
       </c>
@@ -13223,11 +13210,11 @@
         <v>250</v>
       </c>
       <c r="N268" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B268, $C$2:$C$734, C268, $D$2:$D$734, D268, $E$2:$E$734, E268) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="269" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="3">
         <v>46265.415277777778</v>
       </c>
@@ -13269,11 +13256,11 @@
         <v>285</v>
       </c>
       <c r="N269" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B269, $C$2:$C$734, C269, $D$2:$D$734, D269, $E$2:$E$734, E269) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="270" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="3">
         <v>46266.375</v>
       </c>
@@ -13315,11 +13302,11 @@
         <v>726</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B270, $C$2:$C$734, C270, $D$2:$D$734, D270, $E$2:$E$734, E270) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="271" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="8" t="s">
         <v>62</v>
       </c>
@@ -13349,11 +13336,11 @@
       </c>
       <c r="J271" s="36"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B271, $C$2:$C$734, C271, $D$2:$D$734, D271, $E$2:$E$734, E271) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="272" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="8" t="s">
         <v>62</v>
       </c>
@@ -13383,11 +13370,11 @@
       </c>
       <c r="J272" s="36"/>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B272, $C$2:$C$734, C272, $D$2:$D$734, D272, $E$2:$E$734, E272) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="8" t="s">
         <v>62</v>
       </c>
@@ -13417,11 +13404,11 @@
       </c>
       <c r="J273" s="36"/>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B273, $C$2:$C$734, C273, $D$2:$D$734, D273, $E$2:$E$734, E273) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="274" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="8" t="s">
         <v>62</v>
       </c>
@@ -13451,11 +13438,11 @@
       </c>
       <c r="J274" s="36"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B274, $C$2:$C$734, C274, $D$2:$D$734, D274, $E$2:$E$734, E274) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="275" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="8" t="s">
         <v>62</v>
       </c>
@@ -13485,11 +13472,11 @@
       </c>
       <c r="J275" s="36"/>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B275, $C$2:$C$734, C275, $D$2:$D$734, D275, $E$2:$E$734, E275) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="276" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="11">
         <v>46252.6875</v>
       </c>
@@ -13521,11 +13508,11 @@
         <v>118</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B276, $C$2:$C$734, C276, $D$2:$D$734, D276, $E$2:$E$734, E276) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="277" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -13567,11 +13554,11 @@
         <v>275</v>
       </c>
       <c r="N277" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B277, $C$2:$C$734, C277, $D$2:$D$734, D277, $E$2:$E$734, E277) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="278" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="11">
         <v>46252.6875</v>
       </c>
@@ -13606,13 +13593,13 @@
       <c r="L278" s="18"/>
       <c r="M278" s="18"/>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B278, $C$2:$C$734, C278, $D$2:$D$734, D278, $E$2:$E$734, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O278" s="10"/>
       <c r="P278" s="10"/>
     </row>
-    <row r="279" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="11">
         <v>46252.6875</v>
       </c>
@@ -13644,11 +13631,11 @@
         <v>118</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B279, $C$2:$C$734, C279, $D$2:$D$734, D279, $E$2:$E$734, E279) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="280" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="8" t="s">
         <v>62</v>
       </c>
@@ -13678,11 +13665,11 @@
       </c>
       <c r="J280" s="36"/>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B280, $C$2:$C$734, C280, $D$2:$D$734, D280, $E$2:$E$734, E280) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="281" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="8" t="s">
         <v>62</v>
       </c>
@@ -13714,11 +13701,11 @@
         <v>118</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B281, $C$2:$C$734, C281, $D$2:$D$734, D281, $E$2:$E$734, E281) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="282" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="8" t="s">
         <v>62</v>
       </c>
@@ -13753,13 +13740,13 @@
       <c r="L282" s="18"/>
       <c r="M282" s="18"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B282, $C$2:$C$734, C282, $D$2:$D$734, D282, $E$2:$E$734, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O282" s="10"/>
       <c r="P282" s="10"/>
     </row>
-    <row r="283" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="8" t="s">
         <v>62</v>
       </c>
@@ -13789,12 +13776,12 @@
       </c>
       <c r="J283" s="36"/>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B283, $C$2:$C$734, C283, $D$2:$D$734, D283, $E$2:$E$734, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="P283" s="31"/>
     </row>
-    <row r="284" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="3">
         <v>46260.557638888888</v>
       </c>
@@ -13836,12 +13823,12 @@
         <v>250</v>
       </c>
       <c r="N284" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B284, $C$2:$C$734, C284, $D$2:$D$734, D284, $E$2:$E$734, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="P284" s="31"/>
     </row>
-    <row r="285" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="8" t="s">
         <v>62</v>
       </c>
@@ -13871,12 +13858,12 @@
       </c>
       <c r="J285" s="36"/>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B285, $C$2:$C$734, C285, $D$2:$D$734, D285, $E$2:$E$734, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O285" s="31"/>
     </row>
-    <row r="286" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="8" t="s">
         <v>62</v>
       </c>
@@ -13906,11 +13893,11 @@
       </c>
       <c r="J286" s="36"/>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B286, $C$2:$C$734, C286, $D$2:$D$734, D286, $E$2:$E$734, E286) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="287" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="3">
         <v>46260.550694444442</v>
       </c>
@@ -13952,13 +13939,13 @@
         <v>300</v>
       </c>
       <c r="N287" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B287, $C$2:$C$734, C287, $D$2:$D$734, D287, $E$2:$E$734, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O287" s="10"/>
       <c r="P287" s="10"/>
     </row>
-    <row r="288" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="8" t="s">
         <v>62</v>
       </c>
@@ -13993,13 +13980,13 @@
       <c r="L288" s="18"/>
       <c r="M288" s="18"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B288, $C$2:$C$734, C288, $D$2:$D$734, D288, $E$2:$E$734, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O288" s="10"/>
       <c r="P288" s="10"/>
     </row>
-    <row r="289" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -14031,11 +14018,11 @@
         <v>55</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B289, $C$2:$C$734, C289, $D$2:$D$734, D289, $E$2:$E$734, E289) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="290" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="8" t="s">
         <v>62</v>
       </c>
@@ -14065,11 +14052,11 @@
       </c>
       <c r="J290" s="36"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B290, $C$2:$C$734, C290, $D$2:$D$734, D290, $E$2:$E$734, E290) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="291" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="3">
         <v>46259.532638888886</v>
       </c>
@@ -14111,13 +14098,13 @@
         <v>250</v>
       </c>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B291, $C$2:$C$734, C291, $D$2:$D$734, D291, $E$2:$E$734, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O291" s="10"/>
       <c r="P291" s="10"/>
     </row>
-    <row r="292" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="8" t="s">
         <v>62</v>
       </c>
@@ -14147,11 +14134,11 @@
       </c>
       <c r="J292" s="36"/>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B292, $C$2:$C$734, C292, $D$2:$D$734, D292, $E$2:$E$734, E292) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="293" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="53" t="s">
         <v>62</v>
       </c>
@@ -14186,13 +14173,13 @@
       <c r="L293" s="29"/>
       <c r="M293" s="29"/>
       <c r="N293" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B293, $C$2:$C$734, C293, $D$2:$D$734, D293, $E$2:$E$734, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O293" s="31"/>
       <c r="P293" s="31"/>
     </row>
-    <row r="294" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="58">
         <v>46251.506249999999</v>
       </c>
@@ -14227,11 +14214,11 @@
       <c r="L294" s="29"/>
       <c r="M294" s="29"/>
       <c r="N294" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B294, $C$2:$C$734, C294, $D$2:$D$734, D294, $E$2:$E$734, E294) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="295" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="8" t="s">
         <v>62</v>
       </c>
@@ -14266,26 +14253,14 @@
       <c r="L295" s="18"/>
       <c r="M295" s="18"/>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$734, B295, $C$2:$C$734, C295, $D$2:$D$734, D295, $E$2:$E$734, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O295" s="10"/>
       <c r="P295" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P295" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="B"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="14">
-      <filters blank="1"/>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P180">
-      <sortCondition descending="1" ref="F1:F295"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:P1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
